--- a/tmp/dailyReport_Client.xlsx
+++ b/tmp/dailyReport_Client.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87C7795-3D6A-4B0E-99CD-D5F278811434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E7652B-B58B-4CDF-8851-4C32DCE37FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regular service" sheetId="1" r:id="rId1"/>
@@ -224,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -256,7 +256,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -274,7 +274,28 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -783,7 +804,7 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" style="7" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" style="23" customWidth="1"/>
     <col min="2" max="2" width="22.33203125" style="7" customWidth="1"/>
     <col min="3" max="3" width="24.109375" style="8" customWidth="1"/>
     <col min="4" max="4" width="38.33203125" style="8" customWidth="1"/>
@@ -809,7 +830,7 @@
       <c r="E2" s="19"/>
     </row>
     <row r="3" spans="1:5" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="21" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -826,77 +847,77 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
+      <c r="A4" s="22"/>
       <c r="B4" s="2"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
+      <c r="A5" s="22"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
+      <c r="A6" s="22"/>
       <c r="B6" s="2"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
+      <c r="A7" s="22"/>
       <c r="B7" s="2"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="3"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
+      <c r="A8" s="22"/>
       <c r="B8" s="2"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
+      <c r="A9" s="22"/>
       <c r="B9" s="2"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
+      <c r="A10" s="22"/>
       <c r="B10" s="2"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="2"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
+      <c r="A12" s="22"/>
       <c r="B12" s="2"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="2"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
+      <c r="A14" s="22"/>
       <c r="B14" s="2"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -918,7 +939,7 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" customWidth="1"/>
+    <col min="1" max="1" width="19.77734375" style="26" customWidth="1"/>
     <col min="2" max="2" width="20.33203125" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="20.44140625" customWidth="1"/>
@@ -929,16 +950,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
@@ -953,7 +974,7 @@
       <c r="H2" s="15"/>
     </row>
     <row r="3" spans="1:8" s="12" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="24" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="11" t="s">
@@ -979,7 +1000,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="10"/>
+      <c r="A4" s="25"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -989,7 +1010,7 @@
       <c r="H4" s="10"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
+      <c r="A5" s="25"/>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -999,7 +1020,7 @@
       <c r="H5" s="10"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="10"/>
+      <c r="A6" s="25"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -1009,7 +1030,7 @@
       <c r="H6" s="10"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="10"/>
+      <c r="A7" s="25"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
@@ -1019,7 +1040,7 @@
       <c r="H7" s="10"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="10"/>
+      <c r="A8" s="25"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
@@ -1029,7 +1050,7 @@
       <c r="H8" s="10"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="10"/>
+      <c r="A9" s="25"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
@@ -1039,7 +1060,7 @@
       <c r="H9" s="10"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="10"/>
+      <c r="A10" s="25"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -1049,7 +1070,7 @@
       <c r="H10" s="10"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="10"/>
+      <c r="A11" s="25"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
@@ -1059,7 +1080,7 @@
       <c r="H11" s="10"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
+      <c r="A12" s="25"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -1069,7 +1090,7 @@
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="10"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -1079,7 +1100,7 @@
       <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="10"/>
+      <c r="A14" s="25"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
@@ -1103,7 +1124,7 @@
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="26" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -1114,16 +1135,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
@@ -1138,7 +1159,7 @@
       <c r="H2" s="15"/>
     </row>
     <row r="3" spans="1:8" s="13" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="27" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1164,7 +1185,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="10"/>
+      <c r="A4" s="25"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -1174,7 +1195,7 @@
       <c r="H4" s="10"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
+      <c r="A5" s="25"/>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -1184,7 +1205,7 @@
       <c r="H5" s="10"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="10"/>
+      <c r="A6" s="25"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -1194,7 +1215,7 @@
       <c r="H6" s="10"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="10"/>
+      <c r="A7" s="25"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
@@ -1204,7 +1225,7 @@
       <c r="H7" s="10"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="10"/>
+      <c r="A8" s="25"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
@@ -1214,7 +1235,7 @@
       <c r="H8" s="10"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="10"/>
+      <c r="A9" s="25"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
@@ -1224,7 +1245,7 @@
       <c r="H9" s="10"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="10"/>
+      <c r="A10" s="25"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -1234,7 +1255,7 @@
       <c r="H10" s="10"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="10"/>
+      <c r="A11" s="25"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
@@ -1244,7 +1265,7 @@
       <c r="H11" s="10"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
+      <c r="A12" s="25"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -1254,7 +1275,7 @@
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="10"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -1264,7 +1285,7 @@
       <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="10"/>
+      <c r="A14" s="25"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
@@ -1274,7 +1295,7 @@
       <c r="H14" s="10"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="10"/>
+      <c r="A15" s="25"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
@@ -1284,7 +1305,7 @@
       <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="10"/>
+      <c r="A16" s="25"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -1294,7 +1315,7 @@
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="10"/>
+      <c r="A17" s="25"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
@@ -1304,7 +1325,7 @@
       <c r="H17" s="10"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="10"/>
+      <c r="A18" s="25"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -1314,7 +1335,7 @@
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="10"/>
+      <c r="A19" s="25"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>

--- a/tmp/dailyReport_Client.xlsx
+++ b/tmp/dailyReport_Client.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E7652B-B58B-4CDF-8851-4C32DCE37FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82557A2D-63DB-46A6-A00D-A709A120FAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -68,13 +68,19 @@
   </si>
   <si>
     <t>Completed Date</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Images</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,14 +91,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -191,16 +189,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
+      <right style="thin">
         <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -211,12 +202,21 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -226,22 +226,15 @@
   </cellStyleXfs>
   <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -253,32 +246,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -296,6 +265,39 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -318,14 +320,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>929640</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2476500</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1602105</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>984885</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1188719</xdr:rowOff>
     </xdr:to>
@@ -356,7 +358,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5135880" y="0"/>
+          <a:off x="7703820" y="0"/>
           <a:ext cx="3301365" cy="1188719"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -801,132 +803,168 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" style="23" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="24.109375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="38.33203125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="31.5546875" style="9" customWidth="1"/>
+    <col min="1" max="2" width="14.88671875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="24.109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="38.33203125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="31.5546875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:7" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-    </row>
-    <row r="2" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+    </row>
+    <row r="2" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-    </row>
-    <row r="3" spans="1:5" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="1:7" s="25" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="24" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="22"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="G3" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="22"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="22"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="22"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="22"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="14"/>
+    </row>
+    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="22"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="14"/>
+    </row>
+    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="3"/>
       <c r="E14" s="3"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="14"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G15" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -939,7 +977,7 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" style="26" customWidth="1"/>
+    <col min="1" max="1" width="19.77734375" style="15" customWidth="1"/>
     <col min="2" max="2" width="20.33203125" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="20.44140625" customWidth="1"/>
@@ -950,164 +988,164 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-    </row>
-    <row r="3" spans="1:8" s="12" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+    </row>
+    <row r="3" spans="1:8" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="25"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="25"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="25"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="25"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="25"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="25"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="25"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="25"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="25"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="25"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1124,7 +1162,7 @@
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" style="26" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="15" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -1135,214 +1173,214 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-    </row>
-    <row r="3" spans="1:8" s="13" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="27" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+    </row>
+    <row r="3" spans="1:8" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="25"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="25"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="25"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="25"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="25"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="25"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="25"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="25"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="25"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="25"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="25"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="25"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="25"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="25"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="25"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/tmp/dailyReport_Client.xlsx
+++ b/tmp/dailyReport_Client.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82557A2D-63DB-46A6-A00D-A709A120FAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB36E79-D126-4DFB-BD5B-ABD560384E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -74,13 +74,25 @@
   </si>
   <si>
     <t>Images</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Regular services Done </t>
+  </si>
+  <si>
+    <t>Total Regular services Missed</t>
+  </si>
+  <si>
+    <t>Total Regular services Pending</t>
+  </si>
+  <si>
+    <t>Total Locations</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,8 +139,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -138,6 +158,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -224,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -266,6 +292,24 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -281,23 +325,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -803,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="14.88671875" style="12" customWidth="1"/>
@@ -812,153 +841,169 @@
     <col min="5" max="5" width="38.33203125" style="5" customWidth="1"/>
     <col min="6" max="6" width="31.5546875" style="6" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" style="15" customWidth="1"/>
+    <col min="12" max="12" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:15" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-    </row>
-    <row r="2" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+    </row>
+    <row r="2" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-    </row>
-    <row r="3" spans="1:7" s="25" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+    </row>
+    <row r="3" spans="1:15" s="20" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="1"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="22"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="14"/>
     </row>
-    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="1"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="22"/>
+      <c r="F5" s="17"/>
       <c r="G5" s="14"/>
     </row>
-    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="1"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="22"/>
+      <c r="F6" s="17"/>
       <c r="G6" s="14"/>
     </row>
-    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="1"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="22"/>
+      <c r="F7" s="17"/>
       <c r="G7" s="14"/>
-    </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L7" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="1"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="22"/>
+      <c r="F8" s="17"/>
       <c r="G8" s="14"/>
     </row>
-    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="1"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="22"/>
+      <c r="F9" s="17"/>
       <c r="G9" s="14"/>
     </row>
-    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
       <c r="B10" s="11"/>
       <c r="C10" s="1"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="22"/>
+      <c r="F10" s="17"/>
       <c r="G10" s="14"/>
     </row>
-    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="1"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="22"/>
+      <c r="F11" s="17"/>
       <c r="G11" s="14"/>
     </row>
-    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="1"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="22"/>
+      <c r="F12" s="17"/>
       <c r="G12" s="14"/>
     </row>
-    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="1"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="22"/>
+      <c r="F13" s="17"/>
       <c r="G13" s="14"/>
     </row>
-    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11"/>
       <c r="B14" s="11"/>
       <c r="C14" s="1"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="22"/>
+      <c r="F14" s="17"/>
       <c r="G14" s="14"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="G15" s="14"/>
     </row>
   </sheetData>
@@ -988,28 +1033,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -1173,28 +1218,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">

--- a/tmp/dailyReport_Client.xlsx
+++ b/tmp/dailyReport_Client.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB36E79-D126-4DFB-BD5B-ABD560384E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC99885-CB70-45F9-A76B-60F0493CE67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -304,6 +304,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -324,9 +327,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -841,33 +841,33 @@
     <col min="5" max="5" width="38.33203125" style="5" customWidth="1"/>
     <col min="6" max="6" width="31.5546875" style="6" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" style="15" customWidth="1"/>
-    <col min="12" max="12" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.33203125" customWidth="1"/>
     <col min="13" max="13" width="25.77734375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="26.77734375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" spans="1:15" s="20" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
@@ -927,16 +927,16 @@
       <c r="E7" s="3"/>
       <c r="F7" s="17"/>
       <c r="G7" s="14"/>
-      <c r="L7" s="28" t="s">
+      <c r="L7" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="M7" s="28" t="s">
+      <c r="M7" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="N7" s="28" t="s">
+      <c r="N7" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="O7" s="28" t="s">
+      <c r="O7" s="21" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1033,28 +1033,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:8" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -1218,28 +1218,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:8" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">

--- a/tmp/dailyReport_Client.xlsx
+++ b/tmp/dailyReport_Client.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC99885-CB70-45F9-A76B-60F0493CE67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC8FE85-1338-4F33-A4B8-C427C012EF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -918,6 +918,18 @@
       <c r="E6" s="3"/>
       <c r="F6" s="17"/>
       <c r="G6" s="14"/>
+      <c r="L6" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="N6" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="O6" s="21" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
@@ -927,18 +939,6 @@
       <c r="E7" s="3"/>
       <c r="F7" s="17"/>
       <c r="G7" s="14"/>
-      <c r="L7" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="M7" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="N7" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" s="21" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>

--- a/tmp/dailyReport_Client.xlsx
+++ b/tmp/dailyReport_Client.xlsx
@@ -3,21 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC8FE85-1338-4F33-A4B8-C427C012EF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3DB898-6ECE-4CA1-96AD-68EC909F6A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Regular service" sheetId="1" r:id="rId1"/>
-    <sheet name="Unscheduled-Work" sheetId="3" r:id="rId2"/>
-    <sheet name="Complaints" sheetId="2" r:id="rId3"/>
+    <sheet name="Overview" sheetId="5" r:id="rId1"/>
+    <sheet name="Regular service" sheetId="1" r:id="rId2"/>
+    <sheet name="Unscheduled-Work" sheetId="3" r:id="rId3"/>
+    <sheet name="Complaints" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -86,6 +87,24 @@
   </si>
   <si>
     <t>Total Locations</t>
+  </si>
+  <si>
+    <t>Total Services Pending</t>
+  </si>
+  <si>
+    <t>Total Product service Done</t>
+  </si>
+  <si>
+    <t>Total Product services Missed</t>
+  </si>
+  <si>
+    <t>Total Regular Services Pending</t>
+  </si>
+  <si>
+    <t>Total Regular Services Missed</t>
+  </si>
+  <si>
+    <t>Total Regular Services Done</t>
   </si>
 </sst>
 </file>
@@ -250,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -327,6 +346,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -831,6 +853,53 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE57A63-093E-467F-8302-6D7D5C19B553}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1017,7 +1086,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95137C80-9D41-4A1F-AAF8-29130318C828}">
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1202,7 +1271,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01D6A6B-C461-47EF-B4E7-783194B4D6F8}">
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/tmp/dailyReport_Client.xlsx
+++ b/tmp/dailyReport_Client.xlsx
@@ -3,21 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC99885-CB70-45F9-A76B-60F0493CE67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178CD74A-E665-435F-8869-BDA060126277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Regular service" sheetId="1" r:id="rId1"/>
-    <sheet name="Unscheduled-Work" sheetId="3" r:id="rId2"/>
-    <sheet name="Complaints" sheetId="2" r:id="rId3"/>
+    <sheet name="Overview" sheetId="4" r:id="rId1"/>
+    <sheet name="Regular service" sheetId="1" r:id="rId2"/>
+    <sheet name="Unscheduled-Work" sheetId="3" r:id="rId3"/>
+    <sheet name="Complaints" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -76,23 +77,44 @@
     <t>Images</t>
   </si>
   <si>
-    <t xml:space="preserve">Total Regular services Done </t>
-  </si>
-  <si>
-    <t>Total Regular services Missed</t>
-  </si>
-  <si>
-    <t>Total Regular services Pending</t>
-  </si>
-  <si>
-    <t>Total Locations</t>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>Complaints</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total services Done </t>
+  </si>
+  <si>
+    <t>Total services Missed</t>
+  </si>
+  <si>
+    <t>Total services Pending</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Reopened</t>
+  </si>
+  <si>
+    <t>Close Requested</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,8 +169,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -164,6 +194,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -250,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -327,6 +363,21 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -831,8 +882,102 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA547BDA-9582-424D-91B9-FE0D2FA1FAC2}">
+  <dimension ref="A2:N4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="F2" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="31"/>
+      <c r="L3" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="L2:N2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="14.88671875" style="12" customWidth="1"/>
@@ -847,7 +992,7 @@
     <col min="15" max="15" width="13.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>6</v>
       </c>
@@ -858,7 +1003,7 @@
       <c r="F1" s="23"/>
       <c r="G1" s="23"/>
     </row>
-    <row r="2" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>0</v>
       </c>
@@ -869,7 +1014,7 @@
       <c r="F2" s="25"/>
       <c r="G2" s="25"/>
     </row>
-    <row r="3" spans="1:15" s="20" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" s="20" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>4</v>
       </c>
@@ -892,7 +1037,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="1"/>
@@ -901,7 +1046,7 @@
       <c r="F4" s="17"/>
       <c r="G4" s="14"/>
     </row>
-    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="1"/>
@@ -910,7 +1055,7 @@
       <c r="F5" s="17"/>
       <c r="G5" s="14"/>
     </row>
-    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="1"/>
@@ -918,8 +1063,14 @@
       <c r="E6" s="3"/>
       <c r="F6" s="17"/>
       <c r="G6" s="14"/>
-    </row>
-    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="34"/>
+    </row>
+    <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="1"/>
@@ -927,20 +1078,14 @@
       <c r="E7" s="3"/>
       <c r="F7" s="17"/>
       <c r="G7" s="14"/>
-      <c r="L7" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="M7" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="N7" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" s="21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K7" s="34"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="34"/>
+    </row>
+    <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="1"/>
@@ -948,8 +1093,14 @@
       <c r="E8" s="3"/>
       <c r="F8" s="17"/>
       <c r="G8" s="14"/>
-    </row>
-    <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+    </row>
+    <row r="9" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="1"/>
@@ -957,8 +1108,14 @@
       <c r="E9" s="3"/>
       <c r="F9" s="17"/>
       <c r="G9" s="14"/>
-    </row>
-    <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="34"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="34"/>
+      <c r="P9" s="34"/>
+    </row>
+    <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
       <c r="B10" s="11"/>
       <c r="C10" s="1"/>
@@ -966,8 +1123,14 @@
       <c r="E10" s="3"/>
       <c r="F10" s="17"/>
       <c r="G10" s="14"/>
-    </row>
-    <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K10" s="34"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="34"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="34"/>
+      <c r="P10" s="34"/>
+    </row>
+    <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="1"/>
@@ -975,8 +1138,14 @@
       <c r="E11" s="3"/>
       <c r="F11" s="17"/>
       <c r="G11" s="14"/>
-    </row>
-    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K11" s="34"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34"/>
+      <c r="P11" s="34"/>
+    </row>
+    <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="1"/>
@@ -984,8 +1153,14 @@
       <c r="E12" s="3"/>
       <c r="F12" s="17"/>
       <c r="G12" s="14"/>
-    </row>
-    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K12" s="34"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="34"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="34"/>
+      <c r="P12" s="34"/>
+    </row>
+    <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="1"/>
@@ -994,7 +1169,7 @@
       <c r="F13" s="17"/>
       <c r="G13" s="14"/>
     </row>
-    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11"/>
       <c r="B14" s="11"/>
       <c r="C14" s="1"/>
@@ -1003,7 +1178,7 @@
       <c r="F14" s="17"/>
       <c r="G14" s="14"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="G15" s="14"/>
     </row>
   </sheetData>
@@ -1017,7 +1192,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95137C80-9D41-4A1F-AAF8-29130318C828}">
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1202,7 +1377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01D6A6B-C461-47EF-B4E7-783194B4D6F8}">
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/tmp/dailyReport_Client.xlsx
+++ b/tmp/dailyReport_Client.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3DB898-6ECE-4CA1-96AD-68EC909F6A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178CD74A-E665-435F-8869-BDA060126277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="5" r:id="rId1"/>
+    <sheet name="Overview" sheetId="4" r:id="rId1"/>
     <sheet name="Regular service" sheetId="1" r:id="rId2"/>
     <sheet name="Unscheduled-Work" sheetId="3" r:id="rId3"/>
     <sheet name="Complaints" sheetId="2" r:id="rId4"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -77,41 +77,44 @@
     <t>Images</t>
   </si>
   <si>
-    <t xml:space="preserve">Total Regular services Done </t>
-  </si>
-  <si>
-    <t>Total Regular services Missed</t>
-  </si>
-  <si>
-    <t>Total Regular services Pending</t>
-  </si>
-  <si>
-    <t>Total Locations</t>
-  </si>
-  <si>
-    <t>Total Services Pending</t>
-  </si>
-  <si>
-    <t>Total Product service Done</t>
-  </si>
-  <si>
-    <t>Total Product services Missed</t>
-  </si>
-  <si>
-    <t>Total Regular Services Pending</t>
-  </si>
-  <si>
-    <t>Total Regular Services Missed</t>
-  </si>
-  <si>
-    <t>Total Regular Services Done</t>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>Complaints</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total services Done </t>
+  </si>
+  <si>
+    <t>Total services Missed</t>
+  </si>
+  <si>
+    <t>Total services Pending</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Reopened</t>
+  </si>
+  <si>
+    <t>Close Requested</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,8 +169,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -183,6 +194,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -269,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -347,7 +364,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -853,55 +882,102 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE57A63-093E-467F-8302-6D7D5C19B553}">
-  <dimension ref="A1:C4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA547BDA-9582-424D-91B9-FE0D2FA1FAC2}">
+  <dimension ref="A2:N4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="29"/>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="29" t="s">
+        <v>19</v>
+      </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F2" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="F3" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="G3" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="31"/>
+      <c r="L3" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="21" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="29"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
+      <c r="N3" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="L2:N2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="14.88671875" style="12" customWidth="1"/>
@@ -916,7 +992,7 @@
     <col min="15" max="15" width="13.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>6</v>
       </c>
@@ -927,7 +1003,7 @@
       <c r="F1" s="23"/>
       <c r="G1" s="23"/>
     </row>
-    <row r="2" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>0</v>
       </c>
@@ -938,7 +1014,7 @@
       <c r="F2" s="25"/>
       <c r="G2" s="25"/>
     </row>
-    <row r="3" spans="1:15" s="20" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" s="20" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>4</v>
       </c>
@@ -961,7 +1037,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="1"/>
@@ -970,7 +1046,7 @@
       <c r="F4" s="17"/>
       <c r="G4" s="14"/>
     </row>
-    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="1"/>
@@ -979,7 +1055,7 @@
       <c r="F5" s="17"/>
       <c r="G5" s="14"/>
     </row>
-    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="1"/>
@@ -987,20 +1063,14 @@
       <c r="E6" s="3"/>
       <c r="F6" s="17"/>
       <c r="G6" s="14"/>
-      <c r="L6" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="N6" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="O6" s="21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="34"/>
+    </row>
+    <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="1"/>
@@ -1008,8 +1078,14 @@
       <c r="E7" s="3"/>
       <c r="F7" s="17"/>
       <c r="G7" s="14"/>
-    </row>
-    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K7" s="34"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="34"/>
+    </row>
+    <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="1"/>
@@ -1017,8 +1093,14 @@
       <c r="E8" s="3"/>
       <c r="F8" s="17"/>
       <c r="G8" s="14"/>
-    </row>
-    <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+    </row>
+    <row r="9" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="1"/>
@@ -1026,8 +1108,14 @@
       <c r="E9" s="3"/>
       <c r="F9" s="17"/>
       <c r="G9" s="14"/>
-    </row>
-    <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="34"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="34"/>
+      <c r="P9" s="34"/>
+    </row>
+    <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
       <c r="B10" s="11"/>
       <c r="C10" s="1"/>
@@ -1035,8 +1123,14 @@
       <c r="E10" s="3"/>
       <c r="F10" s="17"/>
       <c r="G10" s="14"/>
-    </row>
-    <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K10" s="34"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="34"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="34"/>
+      <c r="P10" s="34"/>
+    </row>
+    <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="1"/>
@@ -1044,8 +1138,14 @@
       <c r="E11" s="3"/>
       <c r="F11" s="17"/>
       <c r="G11" s="14"/>
-    </row>
-    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K11" s="34"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34"/>
+      <c r="P11" s="34"/>
+    </row>
+    <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="1"/>
@@ -1053,8 +1153,14 @@
       <c r="E12" s="3"/>
       <c r="F12" s="17"/>
       <c r="G12" s="14"/>
-    </row>
-    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K12" s="34"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="34"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="34"/>
+      <c r="P12" s="34"/>
+    </row>
+    <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="1"/>
@@ -1063,7 +1169,7 @@
       <c r="F13" s="17"/>
       <c r="G13" s="14"/>
     </row>
-    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11"/>
       <c r="B14" s="11"/>
       <c r="C14" s="1"/>
@@ -1072,7 +1178,7 @@
       <c r="F14" s="17"/>
       <c r="G14" s="14"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="G15" s="14"/>
     </row>
   </sheetData>

--- a/tmp/dailyReport_Client.xlsx
+++ b/tmp/dailyReport_Client.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178CD74A-E665-435F-8869-BDA060126277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDE7805-24F5-4731-9CA0-331B5C651CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>Close Requested</t>
+  </si>
+  <si>
+    <t>Pest Count</t>
   </si>
 </sst>
 </file>
@@ -178,7 +181,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -200,6 +203,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -286,7 +295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -343,41 +352,49 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -400,13 +417,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>2476500</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>984885</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1188719</xdr:rowOff>
@@ -883,7 +900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA547BDA-9582-424D-91B9-FE0D2FA1FAC2}">
-  <dimension ref="A2:N4"/>
+  <dimension ref="A2:N7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
@@ -897,24 +914,24 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="F2" s="30" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="F2" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="29" t="s">
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
@@ -926,22 +943,22 @@
       <c r="C3" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="I3" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="J3" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="31"/>
+      <c r="K3" s="22"/>
       <c r="L3" s="21" t="s">
         <v>22</v>
       </c>
@@ -953,23 +970,50 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="33"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E6" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E7" s="36"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="F2:J2"/>
     <mergeCell ref="L2:N2"/>
+    <mergeCell ref="E6:N6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -981,38 +1025,40 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="14.88671875" style="12" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="24.109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="38.33203125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="31.5546875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" style="15" customWidth="1"/>
-    <col min="12" max="12" width="23.33203125" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="22.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="38.33203125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="31.5546875" style="6" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" style="15" customWidth="1"/>
+    <col min="13" max="13" width="23.33203125" customWidth="1"/>
+    <col min="14" max="14" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
     </row>
     <row r="3" spans="1:16" s="20" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
@@ -1025,15 +1071,18 @@
         <v>3</v>
       </c>
       <c r="D3" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="F3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="G3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="H3" s="18" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1041,150 +1090,123 @@
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="3"/>
+      <c r="D4" s="1"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="14"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="14"/>
     </row>
     <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="3"/>
+      <c r="D5" s="1"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="14"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="14"/>
     </row>
     <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="3"/>
+      <c r="D6" s="1"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="14"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="14"/>
     </row>
     <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="3"/>
+      <c r="D7" s="1"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="14"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
-      <c r="N7" s="35"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="34"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="14"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
     </row>
     <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="3"/>
+      <c r="D8" s="1"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="14"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="14"/>
     </row>
     <row r="9" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="3"/>
+      <c r="D9" s="1"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="14"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="34"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="14"/>
     </row>
     <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
       <c r="B10" s="11"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="3"/>
+      <c r="D10" s="1"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="14"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="34"/>
-      <c r="P10" s="34"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="14"/>
     </row>
     <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="3"/>
+      <c r="D11" s="1"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="14"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="34"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="14"/>
     </row>
     <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="3"/>
+      <c r="D12" s="1"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="14"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="14"/>
     </row>
     <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="3"/>
+      <c r="D13" s="1"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="14"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="14"/>
     </row>
     <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11"/>
       <c r="B14" s="11"/>
       <c r="C14" s="1"/>
-      <c r="D14" s="3"/>
+      <c r="D14" s="1"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="14"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="14"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -1208,28 +1230,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
     </row>
     <row r="3" spans="1:8" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -1393,28 +1415,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
     </row>
     <row r="3" spans="1:8" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">

--- a/tmp/dailyReport_Client.xlsx
+++ b/tmp/dailyReport_Client.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDE7805-24F5-4731-9CA0-331B5C651CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839B38E9-DF1F-4554-9BC0-D3D8B725E7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2808" yWindow="396" windowWidth="13452" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
     <sheet name="Regular service" sheetId="1" r:id="rId2"/>
-    <sheet name="Unscheduled-Work" sheetId="3" r:id="rId3"/>
-    <sheet name="Complaints" sheetId="2" r:id="rId4"/>
+    <sheet name="Complaints" sheetId="2" r:id="rId3"/>
+    <sheet name="Unscheduled-Work" sheetId="3" r:id="rId4"/>
+    <sheet name="Casual-Work" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="41">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -111,13 +112,43 @@
   </si>
   <si>
     <t>Pest Count</t>
+  </si>
+  <si>
+    <t>Floor</t>
+  </si>
+  <si>
+    <t>subLocation</t>
+  </si>
+  <si>
+    <t>Pest Name</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Unscheduled Work</t>
+  </si>
+  <si>
+    <t>Casual Work</t>
+  </si>
+  <si>
+    <t>SubLocation</t>
+  </si>
+  <si>
+    <t>Sub Location</t>
+  </si>
+  <si>
+    <t>Seviced Date</t>
+  </si>
+  <si>
+    <t>Image</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,8 +211,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -191,12 +231,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -212,8 +246,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -291,18 +337,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -316,7 +396,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -325,35 +404,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -361,10 +424,59 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -384,17 +496,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -417,14 +532,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2476500</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1104900</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>984885</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>150919</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1188719</xdr:rowOff>
     </xdr:to>
@@ -455,7 +570,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7703820" y="0"/>
+          <a:off x="10492740" y="0"/>
           <a:ext cx="3301365" cy="1188719"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -469,6 +584,61 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>853440</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1232746</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44A679A4-AD70-4E08-8817-CAC61DD50EFE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8442960" y="0"/>
+          <a:ext cx="2948940" cy="1232746"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -523,27 +693,27 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>419101</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>868681</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1232746</xdr:rowOff>
+      <xdr:rowOff>1181100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44A679A4-AD70-4E08-8817-CAC61DD50EFE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AC10FCC-6A74-4EB7-AB2B-7F3B19D08136}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -565,8 +735,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6979920" y="0"/>
-          <a:ext cx="2948940" cy="1232746"/>
+          <a:off x="7459981" y="0"/>
+          <a:ext cx="3726180" cy="1181100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -900,120 +1070,167 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA547BDA-9582-424D-91B9-FE0D2FA1FAC2}">
-  <dimension ref="A2:N7"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
+    <row r="1" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="38"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="F2" s="27" t="s">
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="G4" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="23" t="s">
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="37"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="B13" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="C13" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="23" t="s">
+      <c r="D13" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="23" t="s">
+      <c r="E13" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="22"/>
-      <c r="L3" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="E6" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="E7" s="36"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="23"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="E6:N6"/>
+  <mergeCells count="5">
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="G4:L4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1021,192 +1238,228 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="14.88671875" style="12" customWidth="1"/>
-    <col min="3" max="4" width="22.33203125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="24.109375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="38.33203125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="31.5546875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" style="15" customWidth="1"/>
-    <col min="13" max="13" width="23.33203125" customWidth="1"/>
-    <col min="14" max="14" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="14.88671875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.21875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="31.5546875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" style="12" customWidth="1"/>
+    <col min="9" max="9" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.33203125" customWidth="1"/>
+    <col min="13" max="13" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:15" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-    </row>
-    <row r="2" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+    </row>
+    <row r="2" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-    </row>
-    <row r="3" spans="1:16" s="20" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+    </row>
+    <row r="3" spans="1:15" s="14" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="H3" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="J3" s="30" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="14"/>
-    </row>
-    <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="14"/>
-    </row>
-    <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="14"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25"/>
-      <c r="P7" s="25"/>
-    </row>
-    <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+    </row>
+    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="14"/>
-    </row>
-    <row r="9" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="14"/>
-    </row>
-    <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="14"/>
-    </row>
-    <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="14"/>
-    </row>
-    <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="14"/>
-    </row>
-    <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="14"/>
-    </row>
-    <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="14"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H15" s="14"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="H15" s="11"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -1215,12 +1468,291 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95137C80-9D41-4A1F-AAF8-29130318C828}">
-  <dimension ref="A1:H14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01D6A6B-C461-47EF-B4E7-783194B4D6F8}">
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" style="15" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="26.44140625" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="31"/>
+    </row>
+    <row r="2" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+    </row>
+    <row r="3" spans="1:11" s="8" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="11"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="11"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="11"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="11"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="11"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="11"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="11"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95137C80-9D41-4A1F-AAF8-29130318C828}">
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="20.44140625" customWidth="1"/>
     <col min="5" max="5" width="13.6640625" customWidth="1"/>
@@ -1229,405 +1761,404 @@
     <col min="8" max="8" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:10" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-    </row>
-    <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+    </row>
+    <row r="2" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-    </row>
-    <row r="3" spans="1:8" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="G3" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="H3" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="I3" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="J3" s="33" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="14"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="11"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="11"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="11"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="11"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="11"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="11"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="11"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01D6A6B-C461-47EF-B4E7-783194B4D6F8}">
-  <dimension ref="A1:H19"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A76C610-A250-48A7-A75A-1EC2AB09712C}">
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="26.44140625" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.77734375" style="51" customWidth="1"/>
+    <col min="2" max="2" width="11.21875" style="50" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" style="50" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" style="50" customWidth="1"/>
+    <col min="5" max="5" width="28" style="50" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" style="50" customWidth="1"/>
+    <col min="7" max="8" width="13.6640625" style="50" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" style="50" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:9" customFormat="1" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-    </row>
-    <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+    </row>
+    <row r="2" spans="1:9" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-    </row>
-    <row r="3" spans="1:8" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+    </row>
+    <row r="3" spans="1:9" s="47" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="E3" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="14"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="14"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="14"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
+      <c r="I3" s="33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="48"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="48"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="48"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="48"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="48"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="48"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="48"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/tmp/dailyReport_Client.xlsx
+++ b/tmp/dailyReport_Client.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178CD74A-E665-435F-8869-BDA060126277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839B38E9-DF1F-4554-9BC0-D3D8B725E7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2808" yWindow="396" windowWidth="13452" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
     <sheet name="Regular service" sheetId="1" r:id="rId2"/>
-    <sheet name="Unscheduled-Work" sheetId="3" r:id="rId3"/>
-    <sheet name="Complaints" sheetId="2" r:id="rId4"/>
+    <sheet name="Complaints" sheetId="2" r:id="rId3"/>
+    <sheet name="Unscheduled-Work" sheetId="3" r:id="rId4"/>
+    <sheet name="Casual-Work" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="41">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -108,13 +109,46 @@
   </si>
   <si>
     <t>Close Requested</t>
+  </si>
+  <si>
+    <t>Pest Count</t>
+  </si>
+  <si>
+    <t>Floor</t>
+  </si>
+  <si>
+    <t>subLocation</t>
+  </si>
+  <si>
+    <t>Pest Name</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Unscheduled Work</t>
+  </si>
+  <si>
+    <t>Casual Work</t>
+  </si>
+  <si>
+    <t>SubLocation</t>
+  </si>
+  <si>
+    <t>Sub Location</t>
+  </si>
+  <si>
+    <t>Seviced Date</t>
+  </si>
+  <si>
+    <t>Image</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,8 +211,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,18 +236,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -282,18 +337,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -307,7 +396,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -316,32 +404,79 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -361,23 +496,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -400,14 +532,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2476500</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1104900</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>984885</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>150919</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1188719</xdr:rowOff>
     </xdr:to>
@@ -438,7 +570,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7703820" y="0"/>
+          <a:off x="10492740" y="0"/>
           <a:ext cx="3301365" cy="1188719"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -452,6 +584,61 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>853440</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1232746</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44A679A4-AD70-4E08-8817-CAC61DD50EFE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8442960" y="0"/>
+          <a:ext cx="2948940" cy="1232746"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -506,27 +693,27 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>419101</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>868681</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1232746</xdr:rowOff>
+      <xdr:rowOff>1181100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44A679A4-AD70-4E08-8817-CAC61DD50EFE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AC10FCC-6A74-4EB7-AB2B-7F3B19D08136}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -548,8 +735,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6979920" y="0"/>
-          <a:ext cx="2948940" cy="1232746"/>
+          <a:off x="7459981" y="0"/>
+          <a:ext cx="3726180" cy="1181100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -883,93 +1070,167 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA547BDA-9582-424D-91B9-FE0D2FA1FAC2}">
-  <dimension ref="A2:N4"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+    <row r="1" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="38"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="F2" s="30" t="s">
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="G4" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="32" t="s">
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="37"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="B13" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="C13" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="D13" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="E13" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="31"/>
-      <c r="L3" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="33"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="23"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="L2:N2"/>
+  <mergeCells count="5">
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="G4:L4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -977,214 +1238,228 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="14.88671875" style="12" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="24.109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="38.33203125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="31.5546875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" style="15" customWidth="1"/>
+    <col min="1" max="2" width="14.88671875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.21875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="31.5546875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" style="12" customWidth="1"/>
+    <col min="9" max="9" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23.33203125" customWidth="1"/>
     <col min="13" max="13" width="25.77734375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="26.77734375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:15" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-    </row>
-    <row r="2" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+    </row>
+    <row r="2" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-    </row>
-    <row r="3" spans="1:16" s="20" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+    </row>
+    <row r="3" spans="1:15" s="14" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="F3" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="H3" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="J3" s="30" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="14"/>
-    </row>
-    <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="14"/>
-    </row>
-    <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="14"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
-    </row>
-    <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="14"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
-      <c r="N7" s="35"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="34"/>
-    </row>
-    <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+    </row>
+    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="14"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-    </row>
-    <row r="9" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="14"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="34"/>
-    </row>
-    <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="14"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="34"/>
-      <c r="P10" s="34"/>
-    </row>
-    <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="14"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="34"/>
-    </row>
-    <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="14"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-    </row>
-    <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="14"/>
-    </row>
-    <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
       <c r="C14" s="1"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="14"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="G15" s="14"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="H15" s="11"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -1193,12 +1468,291 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95137C80-9D41-4A1F-AAF8-29130318C828}">
-  <dimension ref="A1:H14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01D6A6B-C461-47EF-B4E7-783194B4D6F8}">
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" style="15" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="26.44140625" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="31"/>
+    </row>
+    <row r="2" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+    </row>
+    <row r="3" spans="1:11" s="8" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="11"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="11"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="11"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="11"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="11"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="11"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="11"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95137C80-9D41-4A1F-AAF8-29130318C828}">
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="20.44140625" customWidth="1"/>
     <col min="5" max="5" width="13.6640625" customWidth="1"/>
@@ -1207,405 +1761,404 @@
     <col min="8" max="8" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:10" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-    </row>
-    <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+    </row>
+    <row r="2" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-    </row>
-    <row r="3" spans="1:8" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="G3" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="H3" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="I3" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="J3" s="33" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="14"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="11"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="11"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="11"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="11"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="11"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="11"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="11"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01D6A6B-C461-47EF-B4E7-783194B4D6F8}">
-  <dimension ref="A1:H19"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A76C610-A250-48A7-A75A-1EC2AB09712C}">
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="26.44140625" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.77734375" style="51" customWidth="1"/>
+    <col min="2" max="2" width="11.21875" style="50" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" style="50" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" style="50" customWidth="1"/>
+    <col min="5" max="5" width="28" style="50" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" style="50" customWidth="1"/>
+    <col min="7" max="8" width="13.6640625" style="50" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" style="50" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:9" customFormat="1" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-    </row>
-    <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+    </row>
+    <row r="2" spans="1:9" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-    </row>
-    <row r="3" spans="1:8" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+    </row>
+    <row r="3" spans="1:9" s="47" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="E3" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="14"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="14"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="14"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
+      <c r="I3" s="33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="48"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="48"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="48"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="48"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="48"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="48"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="48"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="48"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
